--- a/3- MODELO ENTIDAD RELACIÓN/3- MODELO ENTIDAD RELACIÓN.xlsx
+++ b/3- MODELO ENTIDAD RELACIÓN/3- MODELO ENTIDAD RELACIÓN.xlsx
@@ -8,18 +8,39 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IPLACEX\Año 2\PRÁCTICA IPLACEX\PLATAFORMA PASANTÍAS\GITHUB\3- MODELO ENTIDAD RELACIÓN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D8716C-D818-4B8E-8556-669B3CB28B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D1F4E4-DBE2-46C3-BB77-C3F33C0C7B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" firstSheet="1" activeTab="6" xr2:uid="{36759E41-AA73-48C9-875A-14A402FA6D84}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" firstSheet="5" activeTab="8" xr2:uid="{36759E41-AA73-48C9-875A-14A402FA6D84}"/>
   </bookViews>
   <sheets>
-    <sheet name="PASANTES" sheetId="1" r:id="rId1"/>
-    <sheet name="SOLICITUDES" sheetId="2" r:id="rId2"/>
-    <sheet name="PERIODOS_PASANTIA" sheetId="7" r:id="rId3"/>
-    <sheet name="SERVICIOS" sheetId="3" r:id="rId4"/>
-    <sheet name="JEFATURAS" sheetId="4" r:id="rId5"/>
-    <sheet name="SECRETARIAS" sheetId="5" r:id="rId6"/>
-    <sheet name="TUTORES" sheetId="6" r:id="rId7"/>
+    <sheet name="MODELO ENTIDAD RELACION" sheetId="23" r:id="rId1"/>
+    <sheet name="PASANTES" sheetId="1" r:id="rId2"/>
+    <sheet name="IDENTIFICACION_PASANTES" sheetId="26" r:id="rId3"/>
+    <sheet name="SOLICITUDES" sheetId="2" r:id="rId4"/>
+    <sheet name="ESTADO_SOLICITUDES" sheetId="15" r:id="rId5"/>
+    <sheet name="PERIODOS_PASANTIA" sheetId="7" r:id="rId6"/>
+    <sheet name="TIPO_PASANTIAS" sheetId="14" r:id="rId7"/>
+    <sheet name="TIPO_DOCUMENTOS" sheetId="13" r:id="rId8"/>
+    <sheet name="TIPO_PASANTIA_DOCUMENTOS" sheetId="24" r:id="rId9"/>
+    <sheet name="DOCUMENTOS_SOLICITUDES" sheetId="16" r:id="rId10"/>
+    <sheet name="ESTADO_DOCUMENTOS" sheetId="28" r:id="rId11"/>
+    <sheet name="DOCUMENTOS_FISICOS" sheetId="25" r:id="rId12"/>
+    <sheet name="REQUIERE_INSTITUCION_ORIGEN" sheetId="20" r:id="rId13"/>
+    <sheet name="INSTITUCIONES_ORIGEN" sheetId="19" r:id="rId14"/>
+    <sheet name="GESTOR_INSTITUCION_ORIGEN" sheetId="21" r:id="rId15"/>
+    <sheet name="SERVICIOS" sheetId="3" r:id="rId16"/>
+    <sheet name="JEFATURAS" sheetId="4" r:id="rId17"/>
+    <sheet name="SECRETARIAS" sheetId="5" r:id="rId18"/>
+    <sheet name="TUTORES" sheetId="6" r:id="rId19"/>
+    <sheet name="ADMINISTRADORES" sheetId="8" r:id="rId20"/>
+    <sheet name="ACTIVADORES_QR" sheetId="9" r:id="rId21"/>
+    <sheet name="ROLES" sheetId="10" r:id="rId22"/>
+    <sheet name="ACCESOS_QR" sheetId="11" r:id="rId23"/>
+    <sheet name="GESTION_CREDENCIALES" sheetId="12" r:id="rId24"/>
+    <sheet name="RESOLUCIONES" sheetId="17" r:id="rId25"/>
+    <sheet name="ESTADO RESOLUCIONES" sheetId="18" r:id="rId26"/>
+    <sheet name="NOTIFICACIONES" sheetId="22" r:id="rId27"/>
+    <sheet name="ESTADO_NOTIFICACIONES" sheetId="29" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="274">
   <si>
     <t>campo</t>
   </si>
@@ -81,12 +102,6 @@
     <t>correo</t>
   </si>
   <si>
-    <t>institucion_origen</t>
-  </si>
-  <si>
-    <t>correo_institucion</t>
-  </si>
-  <si>
     <t>profesión</t>
   </si>
   <si>
@@ -138,48 +153,24 @@
     <t>correo electrónico</t>
   </si>
   <si>
-    <t>institución de donde proviene el solicitante</t>
-  </si>
-  <si>
-    <t>correo electrónico de la institución del solicitante</t>
-  </si>
-  <si>
-    <t>identificador único de la solicitud de pasantía</t>
-  </si>
-  <si>
     <t>SOLICITUDES.id</t>
   </si>
   <si>
     <t>id_solicitud</t>
   </si>
   <si>
-    <t>pasante_id</t>
-  </si>
-  <si>
     <t>BIGINT</t>
   </si>
   <si>
     <t>PASANTES.id</t>
   </si>
   <si>
-    <t>servicio_id</t>
-  </si>
-  <si>
     <t>SERVICIOS.id</t>
   </si>
   <si>
-    <t>tutor_id</t>
-  </si>
-  <si>
     <t>TUTORES.id</t>
   </si>
   <si>
-    <t>estado_id</t>
-  </si>
-  <si>
-    <t>ESTADOS_SOLICITUD.id</t>
-  </si>
-  <si>
     <t>DATE</t>
   </si>
   <si>
@@ -189,9 +180,6 @@
     <t>SMALLINT</t>
   </si>
   <si>
-    <t>formulario</t>
-  </si>
-  <si>
     <t>CHAR(1)</t>
   </si>
   <si>
@@ -213,9 +201,6 @@
     <t>identificación del tutor</t>
   </si>
   <si>
-    <t>identificación del estado de la solicitud</t>
-  </si>
-  <si>
     <t>año de la solicitud</t>
   </si>
   <si>
@@ -225,15 +210,9 @@
     <t>nombre_servicio</t>
   </si>
   <si>
-    <t>jefatura_id</t>
-  </si>
-  <si>
     <t>JEFATURAS.id</t>
   </si>
   <si>
-    <t>secretaria_id</t>
-  </si>
-  <si>
     <t>SECRETARIAS.id</t>
   </si>
   <si>
@@ -273,9 +252,6 @@
     <t>estado de la jefatura</t>
   </si>
   <si>
-    <t>identificación del servicio</t>
-  </si>
-  <si>
     <t>identificador</t>
   </si>
   <si>
@@ -300,15 +276,6 @@
     <t>profesión del tutor</t>
   </si>
   <si>
-    <t>fecha_ingreso_solicitud</t>
-  </si>
-  <si>
-    <t>fecha de ingreso de la solicitud en plataforma</t>
-  </si>
-  <si>
-    <t>solicitud_id</t>
-  </si>
-  <si>
     <t>fecha_inicio_solicitada</t>
   </si>
   <si>
@@ -369,30 +336,566 @@
     <t>meses totales de la pasantía, en que equivale un mes a 176 horas</t>
   </si>
   <si>
-    <t>periodo_pasantía</t>
-  </si>
-  <si>
-    <t>identificación del periodo de la pasantía</t>
-  </si>
-  <si>
-    <t>PERIODOS_PASANTIA.id</t>
+    <t>nombre del administrador</t>
+  </si>
+  <si>
+    <t>correo del administrador</t>
+  </si>
+  <si>
+    <t>estado del administrador</t>
+  </si>
+  <si>
+    <t>nombre del activador</t>
+  </si>
+  <si>
+    <t>correo del activador</t>
+  </si>
+  <si>
+    <t>estado del activador</t>
+  </si>
+  <si>
+    <t>rol</t>
+  </si>
+  <si>
+    <t>ROLES.id</t>
+  </si>
+  <si>
+    <t>identificación del rol</t>
+  </si>
+  <si>
+    <t>identificador del rol</t>
+  </si>
+  <si>
+    <t>rol del usuario</t>
+  </si>
+  <si>
+    <t>activado</t>
+  </si>
+  <si>
+    <t>fecha_activacion</t>
+  </si>
+  <si>
+    <t>TIMESTAMP</t>
+  </si>
+  <si>
+    <t>identificador del acceso</t>
+  </si>
+  <si>
+    <t>qr activado</t>
+  </si>
+  <si>
+    <t>fecha de la activación del qr</t>
+  </si>
+  <si>
+    <t>entregada</t>
+  </si>
+  <si>
+    <t>fecha_entrega</t>
+  </si>
+  <si>
+    <t>devuelta</t>
+  </si>
+  <si>
+    <t>fecha_devolucion</t>
+  </si>
+  <si>
+    <t>ADMINISTRADORES.id</t>
+  </si>
+  <si>
+    <t>identificación del administrador</t>
+  </si>
+  <si>
+    <t>activador_qr</t>
+  </si>
+  <si>
+    <t>ACTIVADORES_QR.id</t>
+  </si>
+  <si>
+    <t>identificación del activador del qr</t>
+  </si>
+  <si>
+    <t>solicitud de la pasantúa</t>
+  </si>
+  <si>
+    <t>estado de entrega de la credencial</t>
+  </si>
+  <si>
+    <t>fecha de entrega</t>
+  </si>
+  <si>
+    <t>estado de devolución de la credencial</t>
+  </si>
+  <si>
+    <t>fecha de devolución</t>
+  </si>
+  <si>
+    <t>obligatorio</t>
+  </si>
+  <si>
+    <t>nombre del documento</t>
+  </si>
+  <si>
+    <t>tipo de documento</t>
+  </si>
+  <si>
+    <t>nombre de la pasantía</t>
+  </si>
+  <si>
+    <t>TIPO_PASANTIAS.id</t>
+  </si>
+  <si>
+    <t>identificación del tipo de pasantía</t>
+  </si>
+  <si>
+    <t>descripcion</t>
+  </si>
+  <si>
+    <t>id_estado_solicitud</t>
+  </si>
+  <si>
+    <t>ESTADO_SOLICITUDES.id</t>
+  </si>
+  <si>
+    <t>TIPOS_DOCUMENTOS.id</t>
+  </si>
+  <si>
+    <t>nombre_archivo</t>
+  </si>
+  <si>
+    <t>ruta_archivo</t>
+  </si>
+  <si>
+    <t>VARCHAR(500)</t>
+  </si>
+  <si>
+    <t>fecha_carga</t>
+  </si>
+  <si>
+    <t>identificador del estado de las solicitudes</t>
+  </si>
+  <si>
+    <t>identificador de la solicitud</t>
+  </si>
+  <si>
+    <t>identificador del tipo de documento</t>
+  </si>
+  <si>
+    <t>nombre del archivo</t>
+  </si>
+  <si>
+    <t>ruta (lugar donde se guarda el archivo)</t>
+  </si>
+  <si>
+    <t>fecha de la carga</t>
+  </si>
+  <si>
+    <t>numero_resolucion</t>
+  </si>
+  <si>
+    <t>fecha_resolucion</t>
+  </si>
+  <si>
+    <t>número de la resolución</t>
+  </si>
+  <si>
+    <t>fecha de la resolución</t>
+  </si>
+  <si>
+    <t>nombre del estado de la resolución</t>
+  </si>
+  <si>
+    <t>nombre del estado de las solicitudes</t>
+  </si>
+  <si>
+    <t>id_estado_resolucion</t>
+  </si>
+  <si>
+    <t>ESTADO_RESOLUCIONES.id</t>
+  </si>
+  <si>
+    <t>identificador del estado de las resoluciones</t>
+  </si>
+  <si>
+    <t>nombre de la institución</t>
+  </si>
+  <si>
+    <t>INSTITUCIONES_ORIGEN.id</t>
+  </si>
+  <si>
+    <t>id_institucion_origen</t>
+  </si>
+  <si>
+    <t>identificador de la institución de origen</t>
+  </si>
+  <si>
+    <t>indica si requiere registrar a la institución de origen</t>
+  </si>
+  <si>
+    <t>REQUIERE_INSTITUCION_ORIGEN.id</t>
+  </si>
+  <si>
+    <t>identificador del requerimiento de institución de origen</t>
+  </si>
+  <si>
+    <t>id_gestor_institucion_origen</t>
+  </si>
+  <si>
+    <t>GESTOR_INSTITUCION_ORIGEN.id</t>
+  </si>
+  <si>
+    <t>identificador del gestor de la institución de origen</t>
+  </si>
+  <si>
+    <t>nombre del gestor de la institución de origen</t>
+  </si>
+  <si>
+    <t>correo del gestor de la institución de origen</t>
+  </si>
+  <si>
+    <t>fecha_envio</t>
+  </si>
+  <si>
+    <t>fecha de envío de la notificación</t>
+  </si>
+  <si>
+    <t>1:N</t>
+  </si>
+  <si>
+    <t>1:1</t>
+  </si>
+  <si>
+    <t>relacion</t>
+  </si>
+  <si>
+    <t>PASANTES → SOLICITUDES</t>
+  </si>
+  <si>
+    <t>SERVICIOS → SOLICITUDES</t>
+  </si>
+  <si>
+    <t>TUTORES → SOLICITUDES</t>
+  </si>
+  <si>
+    <t>ESTADO_SOLICITUDES → SOLICITUDES</t>
+  </si>
+  <si>
+    <t>SOLICITUDES → PERIODOS_PASANTIA</t>
+  </si>
+  <si>
+    <t>SOLICITUDES → DOCUMENTOS_SOLICITUDES</t>
+  </si>
+  <si>
+    <t>TIPO_DOCUMENTOS → DOCUMENTOS_SOLICITUDES</t>
+  </si>
+  <si>
+    <t>TIPO_PASANTIAS → SOLICITUDES</t>
+  </si>
+  <si>
+    <t>TIPO_PASANTIAS → TIPO_PASANTIA_DOCUMENTOS</t>
+  </si>
+  <si>
+    <t>TIPO_DOCUMENTOS → TIPO_PASANTIA_DOCUMENTOS</t>
+  </si>
+  <si>
+    <t>REQUIERE_INSTITUCION_ORIGEN → TIPO_PASANTIAS</t>
+  </si>
+  <si>
+    <t>INSTITUCIONES_ORIGEN → SOLICITUDES</t>
+  </si>
+  <si>
+    <t>GESTOR_INSTITUCION_ORIGEN → SOLICITUDES</t>
+  </si>
+  <si>
+    <t>SOLICITUDES → RESOLUCIONES</t>
+  </si>
+  <si>
+    <t>ESTADO_RESOLUCIONES → RESOLUCIONES</t>
+  </si>
+  <si>
+    <t>PASANTES → QR_ACCESOS</t>
+  </si>
+  <si>
+    <t>ACTIVADORES_QR → QR_ACCESOS</t>
+  </si>
+  <si>
+    <t>SOLICITUDES → GESTION_CREDENCIALES</t>
+  </si>
+  <si>
+    <t>ADMINISTRADORES → GESTION_CREDENCIALES</t>
+  </si>
+  <si>
+    <t>SOLICITUDES → NOTIFICACIONES</t>
+  </si>
+  <si>
+    <t>ROLES → JEFATURAS</t>
+  </si>
+  <si>
+    <t>ROLES → SECRETARIAS</t>
+  </si>
+  <si>
+    <t>ROLES → TUTORES</t>
+  </si>
+  <si>
+    <t>ROLES → ADMINISTRADORES</t>
+  </si>
+  <si>
+    <t>ROLES → ACTIVADORES_QR</t>
+  </si>
+  <si>
+    <t>DOCUMENTOS_SOLICITUDES → DOCUMENTOS_FISICOS</t>
+  </si>
+  <si>
+    <t>un pasante puede realizar múltiples solicitudes de pasantía a lo largo del tiempo</t>
+  </si>
+  <si>
+    <t>un servicio o unidad puede recibir múltiples solicitudes de pasantía</t>
+  </si>
+  <si>
+    <t>un tutor puede supervisar múltiples solicitudes de pasantía</t>
+  </si>
+  <si>
+    <t>un estado puede estar asociado a múltiples solicitudes</t>
+  </si>
+  <si>
+    <t>una solicitud puede tener múltiples documentos asociados</t>
+  </si>
+  <si>
+    <t>un tipo documental puede utilizarse en múltiples documentos cargados</t>
+  </si>
+  <si>
+    <t>un tipo de pasantía (A, B, C, D, E) puede estar asociado a múltiples solicitudes</t>
+  </si>
+  <si>
+    <t>un tipo de pasantía puede requerir múltiples documentos</t>
+  </si>
+  <si>
+    <t>un tipo documental puede ser requerido por múltiples tipos de pasantía</t>
+  </si>
+  <si>
+    <t>una regla de obligatoriedad puede aplicarse a múltiples tipos de pasantía</t>
+  </si>
+  <si>
+    <t>una institución de origen puede asociarse a múltiples solicitudes</t>
+  </si>
+  <si>
+    <t>un gestor institucional puede asociarse a múltiples solicitudes</t>
+  </si>
+  <si>
+    <t>un estado de resolución puede estar asociado a múltiples resoluciones</t>
+  </si>
+  <si>
+    <t>un pasante puede tener múltiples activaciones QR históricas asociadas a su cédula de identidad</t>
+  </si>
+  <si>
+    <t>un activador QR puede gestionar múltiples activaciones</t>
+  </si>
+  <si>
+    <t>un administrador puede gestionar múltiples credenciales</t>
+  </si>
+  <si>
+    <t>una solicitud puede generar múltiples notificaciones durante su ciclo de vida</t>
+  </si>
+  <si>
+    <t>un rol puede asignarse a múltiples jefaturas</t>
+  </si>
+  <si>
+    <t>un rol puede asignarse a múltiples secretarias</t>
+  </si>
+  <si>
+    <t>un rol puede asignarse a múltiples tutores</t>
+  </si>
+  <si>
+    <t>un rol puede asignarse a múltiples administradores</t>
+  </si>
+  <si>
+    <t>un rol puede asignarse a múltiples activadores QR</t>
+  </si>
+  <si>
+    <t>un documento lógico puede tener uno o más archivos físicos asociados</t>
+  </si>
+  <si>
+    <t>cada solicitud tiene un único período de pasantía asociado</t>
+  </si>
+  <si>
+    <t>cada solicitud genera una única resolución administrativa</t>
+  </si>
+  <si>
+    <t>cada solicitud tiene una única gestión de credencial</t>
+  </si>
+  <si>
+    <t>tipo de relacion en postgresql</t>
+  </si>
+  <si>
+    <t>TIPO_DOCUMENTOS.id</t>
+  </si>
+  <si>
+    <t>identificación del tipo de documentos</t>
+  </si>
+  <si>
+    <t>definición de la obligatoriedad del documento</t>
+  </si>
+  <si>
+    <t>NOTIFICACIONES.id</t>
+  </si>
+  <si>
+    <t>identificador de la notificación</t>
+  </si>
+  <si>
+    <t>tipo_archivo</t>
+  </si>
+  <si>
+    <t>tamano_archivo</t>
+  </si>
+  <si>
+    <t>NUMERIC(10,2)</t>
+  </si>
+  <si>
+    <t>numero_rut</t>
+  </si>
+  <si>
+    <t>NUMERIC(10)</t>
+  </si>
+  <si>
+    <t>registro_otra_identificacion</t>
+  </si>
+  <si>
+    <t>IDENTIFICACION_PASANTES.id</t>
+  </si>
+  <si>
+    <t>id_identificacion_pasantes</t>
+  </si>
+  <si>
+    <t>tipo de identificación del pasante</t>
+  </si>
+  <si>
+    <t>registro_identificacion</t>
+  </si>
+  <si>
+    <t>id del rut/dni/pasaporte</t>
+  </si>
+  <si>
+    <t>nombre_pasantia</t>
+  </si>
+  <si>
+    <t>tipo_pasantia</t>
+  </si>
+  <si>
+    <t>fecha_registro</t>
+  </si>
+  <si>
+    <t>id_pasante</t>
+  </si>
+  <si>
+    <t>id_servicio</t>
+  </si>
+  <si>
+    <t>id_tutor</t>
+  </si>
+  <si>
+    <t>id_jefatura</t>
+  </si>
+  <si>
+    <t>id_secretaria</t>
+  </si>
+  <si>
+    <t>id_administrador</t>
+  </si>
+  <si>
+    <t>id_pasantia</t>
+  </si>
+  <si>
+    <t>id_documento</t>
+  </si>
+  <si>
+    <t>id_tipo_documento</t>
+  </si>
+  <si>
+    <t>id_notificacion</t>
+  </si>
+  <si>
+    <t>id_requiere_institucion_origen</t>
+  </si>
+  <si>
+    <t>id_destinatario</t>
+  </si>
+  <si>
+    <t>estado</t>
+  </si>
+  <si>
+    <t>completos/incompletos</t>
+  </si>
+  <si>
+    <t>id_estado_documentos</t>
+  </si>
+  <si>
+    <t>ESTADO_DOCUMENTOS.id</t>
+  </si>
+  <si>
+    <t>identificador del estado de los documentos solicitados</t>
+  </si>
+  <si>
+    <t>enviado/pendiente</t>
+  </si>
+  <si>
+    <t>identificación del gestor de la institución</t>
+  </si>
+  <si>
+    <t>ESTADO_NOTIFICACIONES.id</t>
+  </si>
+  <si>
+    <t>identificación de la notificación</t>
+  </si>
+  <si>
+    <t>comentario</t>
+  </si>
+  <si>
+    <t>fecha_solicitud</t>
+  </si>
+  <si>
+    <t>fecha de la solicitud en plataforma</t>
+  </si>
+  <si>
+    <t>id_tipo_pasantia</t>
+  </si>
+  <si>
+    <t>indica si la solicitud o no indentificar a una institución de origen</t>
+  </si>
+  <si>
+    <t>solo se activa si requiere institución de origen</t>
+  </si>
+  <si>
+    <t>identificador del estado de los documentos obligatorios</t>
+  </si>
+  <si>
+    <t>id_estado_notificacion</t>
+  </si>
+  <si>
+    <t>identificador del estado de las notificaciones</t>
+  </si>
+  <si>
+    <t>numero_telefonico</t>
+  </si>
+  <si>
+    <t>número telefónico</t>
+  </si>
+  <si>
+    <t>almacena el año, mes, día, hora, minutos y segundos de cuando se realice o modifique el registro</t>
+  </si>
+  <si>
+    <t>tipo de formato del archivo</t>
+  </si>
+  <si>
+    <t>tamaño del archivo en megabytes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -418,10 +921,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -735,15 +1237,329 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7919348-C299-4579-ADE5-ABC48C6C9CD5}">
-  <dimension ref="A1:F11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{516FF2D8-3FD0-4196-899F-421F1F2C8950}">
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="86.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>173</v>
+      </c>
+      <c r="B8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" t="s">
+        <v>164</v>
+      </c>
+      <c r="C12" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B13" t="s">
+        <v>164</v>
+      </c>
+      <c r="C13" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>179</v>
+      </c>
+      <c r="B14" t="s">
+        <v>164</v>
+      </c>
+      <c r="C14" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>180</v>
+      </c>
+      <c r="B15" t="s">
+        <v>165</v>
+      </c>
+      <c r="C15" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16" t="s">
+        <v>164</v>
+      </c>
+      <c r="C16" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>182</v>
+      </c>
+      <c r="B17" t="s">
+        <v>164</v>
+      </c>
+      <c r="C17" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C18" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B19" t="s">
+        <v>165</v>
+      </c>
+      <c r="C19" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>185</v>
+      </c>
+      <c r="B20" t="s">
+        <v>164</v>
+      </c>
+      <c r="C20" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>186</v>
+      </c>
+      <c r="B21" t="s">
+        <v>164</v>
+      </c>
+      <c r="C21" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>187</v>
+      </c>
+      <c r="B22" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>188</v>
+      </c>
+      <c r="B23" t="s">
+        <v>164</v>
+      </c>
+      <c r="C23" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>189</v>
+      </c>
+      <c r="B24" t="s">
+        <v>164</v>
+      </c>
+      <c r="C24" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>190</v>
+      </c>
+      <c r="B25" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>191</v>
+      </c>
+      <c r="B26" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{022CD96C-AD35-4A5E-82B8-0AF72D468A90}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -771,145 +1587,1129 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>247</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>130</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>253</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>254</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>238</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{007FE1BC-7891-4A4F-AA40-E079FCBC6909}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51CA39EE-A9D8-4BDD-A798-928D35056194}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B6" t="s">
+        <v>227</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55D11AB1-50F8-4EBC-8410-14797263D128}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94DEA8FE-8632-476A-85E8-034C2B45C48C}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CAA14D6-74DC-4CD4-906F-92DA44A8BF4D}">
+  <dimension ref="D1:I5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
         <v>11</v>
       </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E5" t="s">
+        <v>103</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6870329-FF2A-47E9-8BA6-8E49768835E8}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D13B1329-6211-43F1-A077-9B1AE78439AF}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95083019-B2C6-4224-8A38-0ECD6B01FB2A}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95823434-0FAD-4900-884B-A430033FFDE5}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>238</v>
+      </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" t="s">
-        <v>33</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -918,16 +2718,186 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3102D5EA-CEB6-4035-90E3-9CCDF37FEA6F}">
-  <dimension ref="A1:F11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7919348-C299-4579-ADE5-ABC48C6C9CD5}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>269</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>238</v>
+      </c>
+      <c r="B10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{001F0FBA-7855-43CA-AF0B-0135DAF4153A}">
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -955,47 +2925,904 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB4DF014-7696-456C-B4E3-695193C06BDF}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0446AFB-7AA5-42AB-8892-6A4FD563BE48}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC068F27-5CA6-45EB-B6E0-9038B5D28CB6}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5928EF4E-8265-4D31-9896-3011C8517C54}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{790FB7B3-1537-4FE9-B427-8146DB9E8E2C}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D96F229D-65E7-4FFC-BC4A-4C1445947175}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58115495-9496-4202-8B6B-3AF4D9A6B625}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
         <v>54</v>
@@ -1003,110 +3830,594 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>243</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>56</v>
+      <c r="A6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>162</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>86</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>238</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D722C323-6D97-49F6-84C7-70AB01DA7DF5}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AD5A917-5655-4850-9FC7-F9746154F5DC}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
         <v>23</v>
       </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3102D5EA-CEB6-4035-90E3-9CCDF37FEA6F}">
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="42.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>263</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
       <c r="F8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>129</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>249</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>31</v>
+      </c>
+      <c r="D11" t="s">
+        <v>151</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>153</v>
+      </c>
+      <c r="G11" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>253</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>147</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>267</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" t="s">
+        <v>258</v>
+      </c>
+      <c r="E15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>238</v>
+      </c>
+      <c r="B17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -1115,9 +4426,106 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E466EAFF-43E4-4901-8E8A-8693A06556B0}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9D809F9-103F-4834-BA8A-00EA50EA0F66}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
@@ -1153,490 +4561,159 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>107</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6870329-FF2A-47E9-8BA6-8E49768835E8}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D13B1329-6211-43F1-A077-9B1AE78439AF}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95083019-B2C6-4224-8A38-0ECD6B01FB2A}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>76</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>238</v>
+      </c>
+      <c r="B12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -1645,16 +4722,16 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95823434-0FAD-4900-884B-A430033FFDE5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDB00860-3E62-42DD-87CE-4A8EE9DEB551}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1682,75 +4759,275 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>236</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>237</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>249</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>155</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>238</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>74</v>
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85296E24-5867-4327-97FE-6D526A1C173B}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33069381-015E-466E-A42F-166EE647B57E}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>

--- a/3- MODELO ENTIDAD RELACIÓN/3- MODELO ENTIDAD RELACIÓN.xlsx
+++ b/3- MODELO ENTIDAD RELACIÓN/3- MODELO ENTIDAD RELACIÓN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IPLACEX\Año 2\PRÁCTICA IPLACEX\PLATAFORMA PASANTÍAS\GITHUB\3- MODELO ENTIDAD RELACIÓN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F69A9DBF-5473-4042-A268-81645B159E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B181FEE-320B-4DA0-AE05-50A89260DB59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{36759E41-AA73-48C9-875A-14A402FA6D84}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" activeTab="11" xr2:uid="{36759E41-AA73-48C9-875A-14A402FA6D84}"/>
   </bookViews>
   <sheets>
     <sheet name="MODELO ENTIDAD RELACION" sheetId="23" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="164">
   <si>
     <t>campo</t>
   </si>
@@ -143,12 +143,6 @@
     <t>DATE</t>
   </si>
   <si>
-    <t>anio_solicitud</t>
-  </si>
-  <si>
-    <t>SMALLINT</t>
-  </si>
-  <si>
     <t>CHAR(1)</t>
   </si>
   <si>
@@ -170,9 +164,6 @@
     <t>identificación del tutor</t>
   </si>
   <si>
-    <t>año de la solicitud</t>
-  </si>
-  <si>
     <t>a-e según manual del hospital</t>
   </si>
   <si>
@@ -245,21 +236,9 @@
     <t>profesión del tutor</t>
   </si>
   <si>
-    <t>fecha_inicio_solicitada</t>
-  </si>
-  <si>
-    <t>fecha_termino_solicitada</t>
-  </si>
-  <si>
-    <t>hora_inicio_solicitada</t>
-  </si>
-  <si>
     <t>TIME</t>
   </si>
   <si>
-    <t>hora_termino_solicitada</t>
-  </si>
-  <si>
     <t>fecha_inicio_aprobada</t>
   </si>
   <si>
@@ -276,18 +255,6 @@
   </si>
   <si>
     <t>NUMERIC(2,2)</t>
-  </si>
-  <si>
-    <t>fecha de inicio de la pasantía solicitada</t>
-  </si>
-  <si>
-    <t>fecha de término de la pasantía solicitada</t>
-  </si>
-  <si>
-    <t>hora de inicio de la pasantía solicitada</t>
-  </si>
-  <si>
-    <t>hora de término de la pasantía solicitada</t>
   </si>
   <si>
     <t>horas totales de la pasantía</t>
@@ -608,8 +575,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -934,68 +902,68 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" t="s">
         <v>111</v>
       </c>
-      <c r="B1" t="s">
-        <v>122</v>
-      </c>
       <c r="C1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" t="s">
         <v>110</v>
-      </c>
-      <c r="C6" t="s">
-        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1051,12 +1019,12 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -1065,7 +1033,7 @@
         <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1079,52 +1047,52 @@
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1179,12 +1147,12 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -1193,7 +1161,7 @@
         <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1207,52 +1175,52 @@
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1307,12 +1275,12 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
@@ -1321,21 +1289,21 @@
         <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1398,13 +1366,13 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1412,18 +1380,18 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -1432,7 +1400,7 @@
         <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1493,7 +1461,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
@@ -1502,21 +1470,21 @@
         <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
       </c>
       <c r="F11" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1526,7 +1494,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3102D5EA-CEB6-4035-90E3-9CCDF37FEA6F}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
@@ -1558,7 +1526,7 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1575,12 +1543,12 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -1592,12 +1560,12 @@
         <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -1609,12 +1577,12 @@
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
@@ -1626,12 +1594,12 @@
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="B6" t="s">
         <v>30</v>
@@ -1640,180 +1608,189 @@
         <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" t="s">
         <v>31</v>
       </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
       <c r="E7" t="s">
         <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>125</v>
+      <c r="A8" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>65</v>
+      <c r="A9" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>66</v>
+      <c r="A10" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>67</v>
+      <c r="A11" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
         <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
         <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
         <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>152</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>148</v>
+        <v>92</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>26</v>
+      </c>
+      <c r="D16" t="s">
+        <v>91</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F16" t="s">
-        <v>150</v>
+        <v>93</v>
+      </c>
+      <c r="G16" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>26</v>
+      </c>
+      <c r="D17" t="s">
+        <v>95</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>81</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s">
         <v>16</v>
@@ -1822,91 +1799,91 @@
         <v>20</v>
       </c>
       <c r="F19" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>153</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E20" t="s">
         <v>20</v>
       </c>
       <c r="F20" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="E21" t="s">
         <v>20</v>
       </c>
       <c r="F21" t="s">
-        <v>104</v>
-      </c>
-      <c r="G21" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D22" t="s">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="E22" t="s">
         <v>20</v>
       </c>
       <c r="F22" t="s">
-        <v>107</v>
+        <v>150</v>
+      </c>
+      <c r="G22" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E23" t="s">
         <v>20</v>
       </c>
       <c r="F23" t="s">
-        <v>155</v>
+        <v>156</v>
+      </c>
+      <c r="G23" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="E24" t="s">
         <v>20</v>
       </c>
       <c r="F24" t="s">
-        <v>157</v>
+        <v>158</v>
+      </c>
+      <c r="G24" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>99</v>
+        <v>153</v>
       </c>
       <c r="B25" t="s">
         <v>30</v>
@@ -1915,15 +1892,18 @@
         <v>20</v>
       </c>
       <c r="F25" t="s">
-        <v>100</v>
+        <v>156</v>
+      </c>
+      <c r="G25" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="E26" t="s">
         <v>20</v>
@@ -1931,135 +1911,53 @@
       <c r="F26" t="s">
         <v>159</v>
       </c>
+      <c r="G26" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E27" t="s">
         <v>20</v>
       </c>
       <c r="F27" t="s">
+        <v>157</v>
+      </c>
+      <c r="G27" t="s">
         <v>161</v>
-      </c>
-      <c r="G27" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>173</v>
+        <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F28" t="s">
-        <v>167</v>
-      </c>
-      <c r="G28" t="s">
-        <v>174</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>163</v>
+        <v>115</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="E29" t="s">
         <v>20</v>
       </c>
       <c r="F29" t="s">
-        <v>169</v>
-      </c>
-      <c r="G29" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>164</v>
-      </c>
-      <c r="B30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" t="s">
-        <v>20</v>
-      </c>
-      <c r="F30" t="s">
-        <v>167</v>
-      </c>
-      <c r="G30" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>165</v>
-      </c>
-      <c r="B31" t="s">
-        <v>46</v>
-      </c>
-      <c r="E31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F31" t="s">
-        <v>170</v>
-      </c>
-      <c r="G31" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>166</v>
-      </c>
-      <c r="B32" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" t="s">
-        <v>20</v>
-      </c>
-      <c r="F32" t="s">
-        <v>168</v>
-      </c>
-      <c r="G32" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" t="s">
-        <v>35</v>
-      </c>
-      <c r="E33" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>126</v>
-      </c>
-      <c r="B34" t="s">
-        <v>93</v>
-      </c>
-      <c r="E34" t="s">
-        <v>20</v>
-      </c>
-      <c r="F34" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2115,12 +2013,12 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -2129,52 +2027,52 @@
         <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2229,29 +2127,29 @@
         <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
         <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s">
         <v>20</v>
       </c>
       <c r="I3" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -2260,7 +2158,7 @@
         <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="4:9" x14ac:dyDescent="0.25">
@@ -2274,21 +2172,21 @@
         <v>20</v>
       </c>
       <c r="I5" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H6" t="s">
         <v>20</v>
       </c>
       <c r="I6" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2343,12 +2241,12 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
@@ -2357,69 +2255,69 @@
         <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2474,12 +2372,12 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -2488,7 +2386,7 @@
         <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2502,52 +2400,52 @@
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2602,12 +2500,12 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -2616,7 +2514,7 @@
         <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2630,52 +2528,52 @@
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2730,12 +2628,12 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -2744,7 +2642,7 @@
         <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2758,7 +2656,7 @@
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2772,12 +2670,12 @@
         <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -2789,38 +2687,38 @@
         <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
       </c>
       <c r="F8" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
